--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>30.83829715602115</v>
+        <v>30.55094326469016</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>11.90371291182457</v>
+        <v>12.18209721752674</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>25.9799079787846</v>
+        <v>26.2880094123509</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>27.42093054006139</v>
+        <v>27.80232970506856</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.734695430199554</v>
+        <v>4.014262795012042</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>7.268286694463483</v>
+        <v>6.663889794340077</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>61.97589888671864</v>
+        <v>63.17624150343</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.59983050065752</v>
+        <v>25.46303751324943</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>52.69286460826729</v>
+        <v>52.89301743264895</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>46.41956067373302</v>
+        <v>46.67348631596258</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>24.745264159472</v>
+        <v>24.78488357549217</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>9.745264159472004</v>
+        <v>9.784883575492174</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>30.55094326469016</v>
+        <v>30.10675911565919</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.18209721752674</v>
+        <v>11.82496218429791</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>26.2880094123509</v>
+        <v>25.87425883119409</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>27.80232970506856</v>
+        <v>27.48695000427488</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>4.014262795012042</v>
+        <v>3.765835191985542</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.663889794340077</v>
+        <v>6.266804770440595</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>63.17624150343</v>
+        <v>62.57329970629859</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.46303751324943</v>
+        <v>25.62736565946278</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>52.89301743264895</v>
+        <v>53.25500668238929</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>46.67348631596258</v>
+        <v>45.30101704304066</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>24.78488357549217</v>
+        <v>24.38616805995088</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>9.784883575492174</v>
+        <v>9.386168059950883</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>30.10675911565919</v>
+        <v>30.38044731933599</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>11.82496218429791</v>
+        <v>11.84955589220754</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>25.87425883119409</v>
+        <v>26.14199825149709</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>27.48695000427488</v>
+        <v>27.8127498801747</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.765835191985542</v>
+        <v>3.798918230120742</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.266804770440595</v>
+        <v>6.279417419247332</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>62.57329970629859</v>
+        <v>63.97765752562419</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.62736565946278</v>
+        <v>25.66680451089316</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>53.25500668238929</v>
+        <v>53.43786572371441</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>45.30101704304066</v>
+        <v>46.07249853785464</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>24.38616805995088</v>
+        <v>24.60407899279738</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>9.386168059950883</v>
+        <v>9.60407899279738</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>30.38044731933599</v>
+        <v>30.91981583822254</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>11.84955589220754</v>
+        <v>12.10284565570268</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>26.14199825149709</v>
+        <v>26.86560974426665</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>27.8127498801747</v>
+        <v>27.97790405732264</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.798918230120742</v>
+        <v>3.745708170133795</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.279417419247332</v>
+        <v>6.561124074814295</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>63.97765752562419</v>
+        <v>65.06977315627198</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.66680451089316</v>
+        <v>25.89796517263723</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>53.43786572371441</v>
+        <v>55.51214292868444</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>46.07249853785464</v>
+        <v>46.81136958425198</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>24.60407899279738</v>
+        <v>25.07429055564399</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>9.60407899279738</v>
+        <v>10.07429055564399</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>30.91981583822254</v>
+        <v>31.37371142756902</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.10284565570268</v>
+        <v>12.22129420549036</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>26.86560974426665</v>
+        <v>27.25777731213219</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>27.97790405732264</v>
+        <v>28.29527411430956</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.745708170133795</v>
+        <v>3.781952462066612</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.561124074814295</v>
+        <v>6.541864415103491</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>65.06977315627198</v>
+        <v>65.45956812326243</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.89796517263723</v>
+        <v>25.77389827102207</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>55.51214292868444</v>
+        <v>55.11893191627292</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>46.81136958425198</v>
+        <v>47.06961180983877</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>25.07429055564399</v>
+        <v>25.38832638951081</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>10.07429055564399</v>
+        <v>10.38832638951081</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>31.37371142756902</v>
+        <v>31.27734785629839</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.22129420549036</v>
+        <v>11.94426539291831</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>27.25777731213219</v>
+        <v>27.1179386755664</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>28.29527411430956</v>
+        <v>28.18779479570434</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.781952462066612</v>
+        <v>3.750546693328284</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.541864415103491</v>
+        <v>6.493755796538138</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>65.45956812326243</v>
+        <v>65.35516689818547</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.77389827102207</v>
+        <v>25.63524373067688</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>55.11893191627292</v>
+        <v>55.39591147364114</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>47.06961180983877</v>
+        <v>47.33071910812249</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>25.38832638951081</v>
+        <v>25.24672634465962</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>10.38832638951081</v>
+        <v>10.24672634465962</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>31.27734785629839</v>
+        <v>31.21418408132714</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>11.94426539291831</v>
+        <v>12.35379231315254</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>27.1179386755664</v>
+        <v>26.88242571155827</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>28.18779479570434</v>
+        <v>28.26832751737198</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.750546693328284</v>
+        <v>3.770725887040069</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.493755796538138</v>
+        <v>6.523626711130523</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>65.35516689818547</v>
+        <v>65.32260977608811</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.63524373067688</v>
+        <v>26.1990096939654</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>55.39591147364114</v>
+        <v>55.64056218677393</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>47.33071910812249</v>
+        <v>46.55594553195596</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>25.24672634465962</v>
+        <v>25.29715700828988</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>10.24672634465962</v>
+        <v>10.29715700828988</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>31.21418408132714</v>
+        <v>30.8306081772111</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.35379231315254</v>
+        <v>12.12054693242289</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>26.88242571155827</v>
+        <v>26.61587133158465</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>28.26832751737198</v>
+        <v>27.82187394284042</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.770725887040069</v>
+        <v>3.615121403618992</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.523626711130523</v>
+        <v>6.496460025770457</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>65.32260977608811</v>
+        <v>63.75989831008426</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>26.1990096939654</v>
+        <v>25.80580159551041</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>55.64056218677393</v>
+        <v>55.41911880982614</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>46.55594553195596</v>
+        <v>46.02470548957886</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>25.29715700828988</v>
+        <v>24.96185034634252</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>10.29715700828988</v>
+        <v>9.961850346342519</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>30.8306081772111</v>
+        <v>30.83170636799892</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.12054693242289</v>
+        <v>12.07559060521295</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>26.61587133158465</v>
+        <v>26.3950436367386</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>27.82187394284042</v>
+        <v>28.13436075031179</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.615121403618992</v>
+        <v>3.45649872978673</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.496460025770457</v>
+        <v>6.377827476921555</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>63.75989831008426</v>
+        <v>63.31045136371153</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.80580159551041</v>
+        <v>26.15791965366747</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>55.41911880982614</v>
+        <v>55.98198755778883</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>46.02470548957886</v>
+        <v>45.97701149425287</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>24.96185034634252</v>
+        <v>24.94059256949394</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>9.961850346342519</v>
+        <v>9.940592569493937</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>30.83170636799892</v>
+        <v>30.9873384375184</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.07559060521295</v>
+        <v>12.20983571909357</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>26.3950436367386</v>
+        <v>26.66130852948135</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>28.13436075031179</v>
+        <v>28.47305257517166</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.45649872978673</v>
+        <v>3.399834816183669</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.377827476921555</v>
+        <v>6.357035863304858</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>63.31045136371153</v>
+        <v>64.02138798189596</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>26.15791965366747</v>
+        <v>27.8714732138676</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>55.98198755778883</v>
+        <v>53.70906885873124</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>45.97701149425287</v>
+        <v>46.17799343458995</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>24.94059256949394</v>
+        <v>25.11193823570724</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>9.940592569493937</v>
+        <v>10.11193823570724</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>30.9873384375184</v>
+        <v>31.32148813371455</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.20983571909357</v>
+        <v>12.71212292270988</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>26.66130852948135</v>
+        <v>27.42312100083217</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>28.47305257517166</v>
+        <v>28.74046989699501</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.399834816183669</v>
+        <v>3.47481835034125</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.357035863304858</v>
+        <v>6.508204425761418</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>64.02138798189596</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>27.8714732138676</v>
+        <v>28.19183497494654</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>53.70906885873124</v>
+        <v>52.62997278657451</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>46.17799343458995</v>
+        <v>46.64404551298782</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>25.11193823570724</v>
+        <v>25.52457368796249</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>10.11193823570724</v>
+        <v>10.52457368796249</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3850,43 +3850,43 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>31.32148813371455</v>
+        <v>31.7698412396844</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.71212292270988</v>
+        <v>12.85010339424197</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>27.42312100083217</v>
+        <v>27.57719584392217</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>28.74046989699501</v>
+        <v>29.31669857739896</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.47481835034125</v>
+        <v>3.481365627123325</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.508204425761418</v>
+        <v>6.643079918474147</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>64.02138798189596</v>
+        <v>62.35904834721292</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>28.19183497494654</v>
+        <v>28.32589940757197</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>52.62997278657451</v>
+        <v>54.66340355332851</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>46.64404551298782</v>
+        <v>47.40151291875429</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>25.52457368796249</v>
+        <v>25.83813001504732</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>10.52457368796249</v>
+        <v>10.83813001504732</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3850,43 +3850,53 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>31.7698412396844</v>
+        <v>31.59934742169983</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.85010339424197</v>
+        <v>12.86642674364892</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>27.57719584392217</v>
+        <v>27.35108127841317</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>29.31669857739896</v>
+        <v>29.32538758112671</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.481365627123325</v>
+        <v>3.365493050363632</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6.643079918474147</v>
+        <v>6.789568841672764</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>62.35904834721292</v>
+        <v>62.74096022225805</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>28.32589940757197</v>
+        <v>28.93025077394341</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>54.66340355332851</v>
+        <v>54.60699137215893</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>47.40151291875429</v>
+        <v>47.89272030651341</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>25.83813001504732</v>
+        <v>25.74909429973462</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>10.83813001504732</v>
+        <v>10.74909429973462</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3895,8 +3895,44 @@
           <t>2026-10</t>
         </is>
       </c>
+      <c r="B95" s="2" t="n">
+        <v>31.34076778098348</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>12.63459923475434</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>26.40924542808811</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>29.13684153091186</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>3.246679318074436</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>6.729043569468061</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>63.07292297475677</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>28.5294039876469</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>55.09597525991463</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>47.71759097865565</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>25.41798272163214</v>
+      </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>10.41798272163214</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>31.34076778098348</v>
+        <v>31.42382735796702</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.63459923475434</v>
+        <v>12.65037933371531</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>26.40924542808811</v>
+        <v>26.37883170974482</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>29.13684153091186</v>
+        <v>28.81020800700423</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3.246679318074436</v>
+        <v>3.232222094647896</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.729043569468061</v>
+        <v>6.828202221425498</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>63.07292297475677</v>
+        <v>63.04259945409583</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.5294039876469</v>
+        <v>28.06375495739252</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>55.09597525991463</v>
+        <v>55.13041741990207</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>47.71759097865565</v>
+        <v>47.26013644221775</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>25.41798272163214</v>
+        <v>25.41947814718686</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>10.41798272163214</v>
+        <v>10.41947814718686</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>31.42382735796702</v>
+        <v>30.71900218530013</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.65037933371531</v>
+        <v>12.40253516717722</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>26.37883170974482</v>
+        <v>25.60431351214146</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.81020800700423</v>
+        <v>28.55110595836719</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3.232222094647896</v>
+        <v>3.225553488517056</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.828202221425498</v>
+        <v>6.772865126722196</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>63.04259945409583</v>
+        <v>60.40566006288893</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.06375495739252</v>
+        <v>27.94619566216216</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>55.13041741990207</v>
+        <v>54.28208313461429</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>47.26013644221775</v>
+        <v>46.66366858640517</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>25.41947814718686</v>
+        <v>24.86434904719953</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>10.41947814718686</v>
+        <v>9.864349047199529</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.71900218530013</v>
+        <v>30.67002071345764</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.40253516717722</v>
+        <v>12.36216890137681</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.60431351214146</v>
+        <v>25.33807396898424</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.55110595836719</v>
+        <v>28.52092943513471</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3.225553488517056</v>
+        <v>3.210776071271086</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.772865126722196</v>
+        <v>6.785631147694702</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>60.40566006288893</v>
+        <v>59.05629925442231</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>27.94619566216216</v>
+        <v>28.1252775230664</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>54.28208313461429</v>
+        <v>54.69730684269383</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>46.66366858640517</v>
+        <v>46.61464182806684</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.86434904719953</v>
+        <v>24.78077295372537</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.864349047199529</v>
+        <v>9.780772953725371</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.67002071345764</v>
+        <v>30.58116607459022</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.36216890137681</v>
+        <v>12.34041335843408</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.33807396898424</v>
+        <v>25.43184922423584</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.52092943513471</v>
+        <v>28.47032160907007</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3.210776071271086</v>
+        <v>3.116732484457287</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.785631147694702</v>
+        <v>6.722277797421769</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>59.05629925442231</v>
+        <v>59.9472464407604</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.1252775230664</v>
+        <v>28.18230748762821</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>54.69730684269383</v>
+        <v>54.43845127533128</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>46.61464182806684</v>
+        <v>46.07249853785464</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.78077295372537</v>
+        <v>24.74576204210557</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.780772953725371</v>
+        <v>9.745762042105568</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.58116607459022</v>
+        <v>30.86468851002716</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.34041335843408</v>
+        <v>12.74233065120947</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.43184922423584</v>
+        <v>25.86062645035573</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.47032160907007</v>
+        <v>29.08402636646722</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3.116732484457287</v>
+        <v>3.170209410567146</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.722277797421769</v>
+        <v>6.743587611765182</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>59.9472464407604</v>
+        <v>60.92204370215541</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.18230748762821</v>
+        <v>29.10696260240555</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>54.43845127533128</v>
+        <v>54.15985121762744</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>46.07249853785464</v>
+        <v>46.71279858070545</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.74576204210557</v>
+        <v>25.11182671864802</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.745762042105568</v>
+        <v>10.11182671864802</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.86468851002716</v>
+        <v>30.36872235545582</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.74233065120947</v>
+        <v>13.19227691443597</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.86062645035573</v>
+        <v>25.29330705384469</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>29.08402636646722</v>
+        <v>28.7488206388537</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3.170209410567146</v>
+        <v>3.130655041766169</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.743587611765182</v>
+        <v>6.120112204217388</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>60.92204370215541</v>
+        <v>59.60391221114514</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>29.10696260240555</v>
+        <v>28.51964700953895</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>54.15985121762744</v>
+        <v>52.30740869871688</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>46.71279858070545</v>
+        <v>45.48679115435106</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>25.11182671864802</v>
+        <v>24.83979216424381</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>10.11182671864802</v>
+        <v>9.839792164243811</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.36872235545582</v>
+        <v>30.33998123226197</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.19227691443597</v>
+        <v>13.52702678123647</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.29330705384469</v>
+        <v>25.76173674885103</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.7488206388537</v>
+        <v>28.5099719633256</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3.130655041766169</v>
+        <v>3.064567631354942</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.120112204217388</v>
+        <v>6.191361029984174</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>59.60391221114514</v>
+        <v>59.78326199713655</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.51964700953895</v>
+        <v>28.47096205390641</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>52.30740869871688</v>
+        <v>49.97560883983944</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>45.48679115435106</v>
+        <v>43.85905109920326</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.83979216424381</v>
+        <v>24.92534104670613</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.839792164243811</v>
+        <v>9.92534104670613</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.33998123226197</v>
+        <v>30.14240578685059</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.52702678123647</v>
+        <v>13.07496177262659</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.76173674885103</v>
+        <v>25.34368097805018</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.5099719633256</v>
+        <v>28.25352875463207</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3.064567631354942</v>
+        <v>2.916374304942742</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.191361029984174</v>
+        <v>6.201205515522772</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>59.78326199713655</v>
+        <v>58.3001097565887</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.47096205390641</v>
+        <v>28.17278643780131</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>49.97560883983944</v>
+        <v>48.28816813252601</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>43.85905109920326</v>
+        <v>43.00873991077357</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.92534104670613</v>
+        <v>24.5882290286092</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.92534104670613</v>
+        <v>9.588229028609199</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.14240578685059</v>
+        <v>30.31554092796307</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.07496177262659</v>
+        <v>13.07121214206374</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.34368097805018</v>
+        <v>25.53390926125344</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.25352875463207</v>
+        <v>28.38320645402224</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.916374304942742</v>
+        <v>2.891891367550651</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.201205515522772</v>
+        <v>6.225126100778182</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>58.3001097565887</v>
+        <v>59.58766103086401</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.17278643780131</v>
+        <v>28.86016537667135</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>48.28816813252601</v>
+        <v>48.98553475247362</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>43.00873991077357</v>
+        <v>43.63475225408539</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.5882290286092</v>
+        <v>24.73700239696521</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.588229028609199</v>
+        <v>9.737002396965206</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.31554092796307</v>
+        <v>30.51755190125169</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.07121214206374</v>
+        <v>13.30006324463854</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.53390926125344</v>
+        <v>25.71931155171991</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.38320645402224</v>
+        <v>28.40493522451336</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.891891367550651</v>
+        <v>2.919306597406776</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.225126100778182</v>
+        <v>6.343249935707558</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>59.58766103086401</v>
+        <v>60.04057090866268</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.86016537667135</v>
+        <v>29.01581345020594</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>48.98553475247362</v>
+        <v>48.38530965583578</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>43.63475225408539</v>
+        <v>44.45672955105614</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.73700239696521</v>
+        <v>24.92531098807978</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.737002396965206</v>
+        <v>9.925310988079779</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.51755190125169</v>
+        <v>30.12876621445931</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.30006324463854</v>
+        <v>13.1050364403037</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.71931155171991</v>
+        <v>25.49223052525792</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.40493522451336</v>
+        <v>28.12769573544627</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.919306597406776</v>
+        <v>2.889013863702341</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.343249935707558</v>
+        <v>6.193819219911377</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>60.04057090866268</v>
+        <v>59.1255328995037</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>29.01581345020594</v>
+        <v>28.77055299496011</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>48.38530965583578</v>
+        <v>45.41989239452533</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>44.45672955105614</v>
+        <v>42.94213713894117</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.92531098807978</v>
+        <v>24.58602717180332</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.925310988079779</v>
+        <v>9.586027171803323</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30.12876621445931</v>
+        <v>29.77534656261443</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.1050364403037</v>
+        <v>13.1276833926775</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.49223052525792</v>
+        <v>25.24498773103793</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.12769573544627</v>
+        <v>28.17040648155685</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.889013863702341</v>
+        <v>2.869840797959047</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.193819219911377</v>
+        <v>6.094608415894045</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>59.1255328995037</v>
+        <v>57.80155464362131</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.77055299496011</v>
+        <v>28.55382566543122</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>45.41989239452533</v>
+        <v>44.8425208810356</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>42.94213713894117</v>
+        <v>42.67777615616969</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.58602717180332</v>
+        <v>24.3764647156648</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.586027171803323</v>
+        <v>9.376464715664799</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>29.77534656261443</v>
+        <v>29.68141158271729</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.1276833926775</v>
+        <v>13.20182961314302</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.24498773103793</v>
+        <v>25.41303868486881</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.17040648155685</v>
+        <v>28.09574757180923</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.869840797959047</v>
+        <v>2.873898830761591</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.094608415894045</v>
+        <v>6.119311980341314</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>57.80155464362131</v>
+        <v>57.43697190736719</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.55382566543122</v>
+        <v>29.0259129327852</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>44.8425208810356</v>
+        <v>46.66152966456967</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>42.67777615616969</v>
+        <v>40.33437826541275</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.3764647156648</v>
+        <v>24.37067679133566</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.376464715664799</v>
+        <v>9.370676791335658</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>29.68141158271729</v>
+        <v>29.7242213109616</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.20182961314302</v>
+        <v>13.42344772180129</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.41303868486881</v>
+        <v>25.55670061138249</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.09574757180923</v>
+        <v>28.30336811405621</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.873898830761591</v>
+        <v>2.915955886821517</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.119311980341314</v>
+        <v>6.120112204217388</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>57.43697190736719</v>
+        <v>57.96508127686293</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>29.0259129327852</v>
+        <v>29.3218874317482</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46.66152966456967</v>
+        <v>48.14756564114832</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>40.33437826541275</v>
+        <v>41.05850091796597</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.37067679133566</v>
+        <v>24.51874088516733</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.370676791335658</v>
+        <v>9.518740885167325</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>29.7242213109616</v>
+        <v>29.61033540555561</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.42344772180129</v>
+        <v>13.4056813939342</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.55670061138249</v>
+        <v>25.48277705402553</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.30336811405621</v>
+        <v>28.23337357646498</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.915955886821517</v>
+        <v>2.886551985676178</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.120112204217388</v>
+        <v>5.999294709095034</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>57.96508127686293</v>
+        <v>57.57315018638889</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>29.3218874317482</v>
+        <v>29.18335882970845</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>48.14756564114832</v>
+        <v>48.18263944602259</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>41.05850091796597</v>
+        <v>39.44507120550679</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.51874088516733</v>
+        <v>24.42308837392534</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.518740885167325</v>
+        <v>9.423088373925335</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>29.61033540555561</v>
+        <v>29.24220691132438</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.4056813939342</v>
+        <v>13.12957417236822</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.48277705402553</v>
+        <v>25.09563092684437</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.23337357646498</v>
+        <v>27.81144693115005</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.886551985676178</v>
+        <v>2.875118479437823</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>5.999294709095034</v>
+        <v>6.017034973727227</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>57.57315018638889</v>
+        <v>57.0471621267377</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>29.18335882970845</v>
+        <v>28.88015510160758</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>48.18263944602259</v>
+        <v>46.79357502619562</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>39.44507120550679</v>
+        <v>38.67487455714263</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.42308837392534</v>
+        <v>24.06739973565859</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.423088373925335</v>
+        <v>9.067399735658594</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>29.24220691132438</v>
+        <v>29.02841654622046</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>13.12957417236822</v>
+        <v>12.91381689740085</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>25.09563092684437</v>
+        <v>24.80932074658287</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>27.81144693115005</v>
+        <v>27.9410338491236</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.875118479437823</v>
+        <v>2.795627583376338</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.017034973727227</v>
+        <v>5.990847161501582</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>57.0471621267377</v>
+        <v>56.45281852269645</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.88015510160758</v>
+        <v>28.79041873153526</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46.79357502619562</v>
+        <v>47.56757878427005</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>38.67487455714263</v>
+        <v>39.22190248581509</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>24.06739973565859</v>
+        <v>23.8894057397635</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>9.067399735658594</v>
+        <v>8.889405739763497</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>29.02841654622046</v>
+        <v>29.04790001259151</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.91381689740085</v>
+        <v>12.82659821003976</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>24.80932074658287</v>
+        <v>24.75569443183416</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>27.9410338491236</v>
+        <v>27.8088413993034</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.795627583376338</v>
+        <v>2.69266196756041</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>5.990847161501582</v>
+        <v>6.020130952617747</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>56.45281852269645</v>
+        <v>56.56971823318349</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.79041873153526</v>
+        <v>28.9805205407096</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>47.56757878427005</v>
+        <v>48.17386620504552</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>39.22190248581509</v>
+        <v>39.40303382944407</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>23.8894057397635</v>
+        <v>23.8669185428687</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>8.889405739763497</v>
+        <v>8.866918542868699</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3896,43 +3896,43 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>29.04790001259151</v>
+        <v>29.33337822201442</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.82659821003976</v>
+        <v>13.1999179668046</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>24.75569443183416</v>
+        <v>24.90282547071293</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>27.8088413993034</v>
+        <v>27.86235256921806</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2.69266196756041</v>
+        <v>2.649832142261535</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>6.020130952617747</v>
+        <v>6.063811612548635</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>56.56971823318349</v>
+        <v>56.78037882762592</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.9805205407096</v>
+        <v>29.17825327358009</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>48.17386620504552</v>
+        <v>50.31777732942374</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>39.40303382944407</v>
+        <v>39.99983419757845</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>23.8669185428687</v>
+        <v>24.14872473029646</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>8.866918542868699</v>
+        <v>9.148724730296461</v>
       </c>
     </row>
   </sheetData>
